--- a/ResourcesPK/LmtOrderCreationExcel.xlsx
+++ b/ResourcesPK/LmtOrderCreationExcel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="182">
   <si>
     <t>PO_NUMBER</t>
   </si>
@@ -264,6 +264,312 @@
   </si>
   <si>
     <t>F4CC3</t>
+  </si>
+  <si>
+    <t>C7726</t>
+  </si>
+  <si>
+    <t>7E719</t>
+  </si>
+  <si>
+    <t>B762C</t>
+  </si>
+  <si>
+    <t>9B049</t>
+  </si>
+  <si>
+    <t>0F41A</t>
+  </si>
+  <si>
+    <t>B4836</t>
+  </si>
+  <si>
+    <t>2E05F</t>
+  </si>
+  <si>
+    <t>FF968</t>
+  </si>
+  <si>
+    <t>237F5</t>
+  </si>
+  <si>
+    <t>CC997</t>
+  </si>
+  <si>
+    <t>F2CC3</t>
+  </si>
+  <si>
+    <t>06CEF</t>
+  </si>
+  <si>
+    <t>C7CFD</t>
+  </si>
+  <si>
+    <t>CA3F9</t>
+  </si>
+  <si>
+    <t>E8501</t>
+  </si>
+  <si>
+    <t>F60D0</t>
+  </si>
+  <si>
+    <t>ED09C</t>
+  </si>
+  <si>
+    <t>A143B</t>
+  </si>
+  <si>
+    <t>8063D</t>
+  </si>
+  <si>
+    <t>D5724</t>
+  </si>
+  <si>
+    <t>30FBA</t>
+  </si>
+  <si>
+    <t>51C5A</t>
+  </si>
+  <si>
+    <t>0FAD2</t>
+  </si>
+  <si>
+    <t>761F1</t>
+  </si>
+  <si>
+    <t>D3ED1</t>
+  </si>
+  <si>
+    <t>F168E</t>
+  </si>
+  <si>
+    <t>FA410</t>
+  </si>
+  <si>
+    <t>1EA16</t>
+  </si>
+  <si>
+    <t>0D88D</t>
+  </si>
+  <si>
+    <t>F4E4E</t>
+  </si>
+  <si>
+    <t>1A5EC</t>
+  </si>
+  <si>
+    <t>DBE13</t>
+  </si>
+  <si>
+    <t>58980</t>
+  </si>
+  <si>
+    <t>B1E98</t>
+  </si>
+  <si>
+    <t>7A941</t>
+  </si>
+  <si>
+    <t>BB685</t>
+  </si>
+  <si>
+    <t>03207</t>
+  </si>
+  <si>
+    <t>4F5EF</t>
+  </si>
+  <si>
+    <t>E1076</t>
+  </si>
+  <si>
+    <t>37B4C</t>
+  </si>
+  <si>
+    <t>8D084</t>
+  </si>
+  <si>
+    <t>F36E8</t>
+  </si>
+  <si>
+    <t>B5B3A</t>
+  </si>
+  <si>
+    <t>5651D</t>
+  </si>
+  <si>
+    <t>E9380</t>
+  </si>
+  <si>
+    <t>03931</t>
+  </si>
+  <si>
+    <t>59EE1</t>
+  </si>
+  <si>
+    <t>D7353</t>
+  </si>
+  <si>
+    <t>C997C</t>
+  </si>
+  <si>
+    <t>B138C</t>
+  </si>
+  <si>
+    <t>4B95E</t>
+  </si>
+  <si>
+    <t>68FF5</t>
+  </si>
+  <si>
+    <t>7FF00</t>
+  </si>
+  <si>
+    <t>2ECCD</t>
+  </si>
+  <si>
+    <t>E0991</t>
+  </si>
+  <si>
+    <t>9EA91</t>
+  </si>
+  <si>
+    <t>C0FB6</t>
+  </si>
+  <si>
+    <t>CAD54</t>
+  </si>
+  <si>
+    <t>7F34F</t>
+  </si>
+  <si>
+    <t>E9389</t>
+  </si>
+  <si>
+    <t>9B9A8</t>
+  </si>
+  <si>
+    <t>49CA0</t>
+  </si>
+  <si>
+    <t>A3C19</t>
+  </si>
+  <si>
+    <t>A2FD6</t>
+  </si>
+  <si>
+    <t>22081</t>
+  </si>
+  <si>
+    <t>23868</t>
+  </si>
+  <si>
+    <t>F3E3C</t>
+  </si>
+  <si>
+    <t>CEEDE</t>
+  </si>
+  <si>
+    <t>3CE1F</t>
+  </si>
+  <si>
+    <t>D7B8A</t>
+  </si>
+  <si>
+    <t>513D8</t>
+  </si>
+  <si>
+    <t>B6F75</t>
+  </si>
+  <si>
+    <t>13A5A</t>
+  </si>
+  <si>
+    <t>70448</t>
+  </si>
+  <si>
+    <t>E2F45</t>
+  </si>
+  <si>
+    <t>36F5E</t>
+  </si>
+  <si>
+    <t>F6F96</t>
+  </si>
+  <si>
+    <t>012AF</t>
+  </si>
+  <si>
+    <t>AA06D</t>
+  </si>
+  <si>
+    <t>A80D4</t>
+  </si>
+  <si>
+    <t>54E4B</t>
+  </si>
+  <si>
+    <t>5140D</t>
+  </si>
+  <si>
+    <t>60AF1</t>
+  </si>
+  <si>
+    <t>601DF</t>
+  </si>
+  <si>
+    <t>111C2</t>
+  </si>
+  <si>
+    <t>9CF58</t>
+  </si>
+  <si>
+    <t>93911</t>
+  </si>
+  <si>
+    <t>C1F53</t>
+  </si>
+  <si>
+    <t>481E3</t>
+  </si>
+  <si>
+    <t>5B35D</t>
+  </si>
+  <si>
+    <t>29AA4</t>
+  </si>
+  <si>
+    <t>1B06E</t>
+  </si>
+  <si>
+    <t>2E85D</t>
+  </si>
+  <si>
+    <t>9AB92</t>
+  </si>
+  <si>
+    <t>CD006</t>
+  </si>
+  <si>
+    <t>628D2</t>
+  </si>
+  <si>
+    <t>24BEF</t>
+  </si>
+  <si>
+    <t>5CC87</t>
+  </si>
+  <si>
+    <t>DB557</t>
+  </si>
+  <si>
+    <t>C421A</t>
+  </si>
+  <si>
+    <t>70D15</t>
+  </si>
+  <si>
+    <t>4DF1C</t>
   </si>
 </sst>
 </file>
@@ -647,7 +953,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -673,7 +979,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>79</v>
+        <v>181</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>10</v>

--- a/ResourcesPK/LmtOrderCreationExcel.xlsx
+++ b/ResourcesPK/LmtOrderCreationExcel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="190">
   <si>
     <t>PO_NUMBER</t>
   </si>
@@ -570,6 +570,30 @@
   </si>
   <si>
     <t>4DF1C</t>
+  </si>
+  <si>
+    <t>94891</t>
+  </si>
+  <si>
+    <t>94211</t>
+  </si>
+  <si>
+    <t>D4B3C</t>
+  </si>
+  <si>
+    <t>C81D9</t>
+  </si>
+  <si>
+    <t>EFFFF</t>
+  </si>
+  <si>
+    <t>EA6BE</t>
+  </si>
+  <si>
+    <t>91E41</t>
+  </si>
+  <si>
+    <t>5551B</t>
   </si>
 </sst>
 </file>
@@ -953,7 +977,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -979,7 +1003,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>10</v>

--- a/ResourcesPK/LmtOrderCreationExcel.xlsx
+++ b/ResourcesPK/LmtOrderCreationExcel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="194">
   <si>
     <t>PO_NUMBER</t>
   </si>
@@ -594,6 +594,18 @@
   </si>
   <si>
     <t>5551B</t>
+  </si>
+  <si>
+    <t>4AEAA</t>
+  </si>
+  <si>
+    <t>FC5BA</t>
+  </si>
+  <si>
+    <t>02B84</t>
+  </si>
+  <si>
+    <t>DF844</t>
   </si>
 </sst>
 </file>
@@ -977,7 +989,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
@@ -1003,7 +1015,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>10</v>

--- a/ResourcesPK/LmtOrderCreationExcel.xlsx
+++ b/ResourcesPK/LmtOrderCreationExcel.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="153222"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\ExcelGenerator\ResourcesPK\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Huzaifa\JAR\ResourcesPK\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,7 +16,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
   <si>
     <t>PO_NUMBER</t>
   </si>
@@ -59,22 +59,125 @@
     <t>50250327</t>
   </si>
   <si>
-    <t>7EC57</t>
-  </si>
-  <si>
-    <t>967D4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21021066 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20014766 </t>
+    <t>7AEFE</t>
+  </si>
+  <si>
+    <t>84FBE</t>
+  </si>
+  <si>
+    <t>21021066</t>
+  </si>
+  <si>
+    <t>20014766</t>
+  </si>
+  <si>
+    <t>38A51</t>
+  </si>
+  <si>
+    <t>55ACB</t>
+  </si>
+  <si>
+    <t>B1619</t>
+  </si>
+  <si>
+    <t>6805B</t>
+  </si>
+  <si>
+    <t>69331</t>
+  </si>
+  <si>
+    <t>BA918</t>
+  </si>
+  <si>
+    <t>052A4</t>
+  </si>
+  <si>
+    <t>BF2CC</t>
+  </si>
+  <si>
+    <t>E89EA</t>
+  </si>
+  <si>
+    <t>0BE1C</t>
+  </si>
+  <si>
+    <t>CBE15</t>
+  </si>
+  <si>
+    <t>C98A2</t>
+  </si>
+  <si>
+    <t>AFADD</t>
+  </si>
+  <si>
+    <t>13A22</t>
+  </si>
+  <si>
+    <t>4B57F</t>
+  </si>
+  <si>
+    <t>2334A</t>
+  </si>
+  <si>
+    <t>E677B</t>
+  </si>
+  <si>
+    <t>3F1BD</t>
+  </si>
+  <si>
+    <t>6F36D</t>
+  </si>
+  <si>
+    <t>2D276</t>
+  </si>
+  <si>
+    <t>F6FBC</t>
+  </si>
+  <si>
+    <t>ECD31</t>
+  </si>
+  <si>
+    <t>0F8B1</t>
+  </si>
+  <si>
+    <t>F5F6C</t>
+  </si>
+  <si>
+    <t>96DC5</t>
+  </si>
+  <si>
+    <t>267AC</t>
+  </si>
+  <si>
+    <t>6FDD0</t>
+  </si>
+  <si>
+    <t>FD676</t>
+  </si>
+  <si>
+    <t>37D9E</t>
+  </si>
+  <si>
+    <t>A9053</t>
+  </si>
+  <si>
+    <t>CE8CF</t>
+  </si>
+  <si>
+    <t>587DA</t>
+  </si>
+  <si>
+    <t>3AA51</t>
+  </si>
+  <si>
+    <t>7D569</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -411,16 +514,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.1796875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="22.54296875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" style="3" customWidth="1"/>
-    <col min="5" max="5" width="15.453125" customWidth="1"/>
-    <col min="6" max="6" width="14.7265625" customWidth="1"/>
-    <col min="7" max="7" width="14.26953125" customWidth="1"/>
-    <col min="8" max="8" width="12.81640625" style="3" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" style="3" width="26.140625"/>
+    <col min="2" max="2" customWidth="true" style="3" width="22.5703125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="3" width="12.28515625"/>
+    <col min="4" max="4" customWidth="true" style="3" width="19.0"/>
+    <col min="5" max="5" customWidth="true" width="15.42578125"/>
+    <col min="6" max="6" customWidth="true" width="14.7109375"/>
+    <col min="7" max="7" customWidth="true" width="14.28515625"/>
+    <col min="8" max="8" customWidth="true" style="3" width="12.85546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -451,7 +554,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>9</v>
@@ -462,13 +565,13 @@
       <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="0">
         <v>1</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="0">
         <v>0</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="0">
         <v>10</v>
       </c>
       <c r="H2" s="3" t="s">
@@ -477,7 +580,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
@@ -488,13 +591,13 @@
       <c r="D3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="0">
         <v>1</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="0">
         <v>0</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="0">
         <v>10</v>
       </c>
       <c r="H3" s="3" t="s">

--- a/ResourcesPK/LmtOrderCreationExcel.xlsx
+++ b/ResourcesPK/LmtOrderCreationExcel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="59">
   <si>
     <t>PO_NUMBER</t>
   </si>
@@ -171,6 +171,36 @@
   </si>
   <si>
     <t>7D569</t>
+  </si>
+  <si>
+    <t>58660</t>
+  </si>
+  <si>
+    <t>450B5</t>
+  </si>
+  <si>
+    <t>FB605</t>
+  </si>
+  <si>
+    <t>C7052</t>
+  </si>
+  <si>
+    <t>F8A6C</t>
+  </si>
+  <si>
+    <t>159B9</t>
+  </si>
+  <si>
+    <t>9B38C</t>
+  </si>
+  <si>
+    <t>03EBE</t>
+  </si>
+  <si>
+    <t>140B0</t>
+  </si>
+  <si>
+    <t>1F4B3</t>
   </si>
 </sst>
 </file>
@@ -554,7 +584,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>9</v>
@@ -580,7 +610,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>

--- a/ResourcesPK/LmtOrderCreationExcel.xlsx
+++ b/ResourcesPK/LmtOrderCreationExcel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="83">
   <si>
     <t>PO_NUMBER</t>
   </si>
@@ -201,6 +201,78 @@
   </si>
   <si>
     <t>1F4B3</t>
+  </si>
+  <si>
+    <t>5898E</t>
+  </si>
+  <si>
+    <t>CD347</t>
+  </si>
+  <si>
+    <t>3EAFF</t>
+  </si>
+  <si>
+    <t>403AF</t>
+  </si>
+  <si>
+    <t>3A693</t>
+  </si>
+  <si>
+    <t>4699B</t>
+  </si>
+  <si>
+    <t>3377C</t>
+  </si>
+  <si>
+    <t>BA8F5</t>
+  </si>
+  <si>
+    <t>F9F3B</t>
+  </si>
+  <si>
+    <t>696DC</t>
+  </si>
+  <si>
+    <t>FC4EE</t>
+  </si>
+  <si>
+    <t>FBEE8</t>
+  </si>
+  <si>
+    <t>EBFCB</t>
+  </si>
+  <si>
+    <t>05F3B</t>
+  </si>
+  <si>
+    <t>D2165</t>
+  </si>
+  <si>
+    <t>C14DF</t>
+  </si>
+  <si>
+    <t>2766D</t>
+  </si>
+  <si>
+    <t>0142C</t>
+  </si>
+  <si>
+    <t>D80C2</t>
+  </si>
+  <si>
+    <t>2513C</t>
+  </si>
+  <si>
+    <t>885FC</t>
+  </si>
+  <si>
+    <t>AFBDB</t>
+  </si>
+  <si>
+    <t>F7C77</t>
+  </si>
+  <si>
+    <t>FDE88</t>
   </si>
 </sst>
 </file>
@@ -584,7 +656,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="3" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>9</v>
@@ -610,7 +682,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="3" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>9</v>
